--- a/data/b2_primavera/B2 Primavera 03-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 03-2026.xlsx
@@ -4891,79 +4891,79 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>518.4400000000001</v>
+        <v>495.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>58468.85</v>
+        <v>1045.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>711.8200000000001</v>
+        <v>57091.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46089</v>
+        <v>46087</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3804.73</v>
+        <v>2558.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46091</v>
+        <v>46089</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>14000</v>
+        <v>4047.13</v>
       </c>
     </row>
     <row r="7">
@@ -4972,34 +4972,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3600</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1405.55</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="9">
@@ -5017,25 +5017,25 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1215.86</v>
+        <v>1296.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46096</v>
+        <v>46094</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9712.66</v>
+        <v>1056.14</v>
       </c>
     </row>
     <row r="11">
@@ -5044,16 +5044,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1639.49</v>
+        <v>8737.41</v>
       </c>
     </row>
     <row r="12">
@@ -5062,106 +5062,106 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3894.81</v>
+        <v>1519.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1890.26</v>
+        <v>3929.46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>20234.86</v>
+        <v>2117.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46103</v>
+        <v>46100</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3896.96</v>
+        <v>1053.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46105</v>
+        <v>46101</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1486.12</v>
+        <v>20356.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46106</v>
+        <v>46103</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>1179.78</v>
+        <v>3925.31</v>
       </c>
     </row>
     <row r="18">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3911.29</v>
+        <v>3946.34</v>
       </c>
     </row>
     <row r="19">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>1001.83</v>
+        <v>1045.62</v>
       </c>
     </row>
   </sheetData>
